--- a/docs/assets/literature_overview.xlsx
+++ b/docs/assets/literature_overview.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\GE\Faggrupper\LTES\Cross country projects 2025\LAVA-tool\literature\China\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE762A6-E6E0-48DE-92F4-D808BF365FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0315CB1D-0033-4479-B617-3E0DB893DFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{B59307C2-C4D5-44E9-B8B3-D82350FA2CB1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B59307C2-C4D5-44E9-B8B3-D82350FA2CB1}"/>
   </bookViews>
   <sheets>
-    <sheet name="solarPV" sheetId="1" r:id="rId1"/>
-    <sheet name="sources" sheetId="3" r:id="rId2"/>
+    <sheet name="sources" sheetId="3" r:id="rId1"/>
+    <sheet name="solarPV" sheetId="1" r:id="rId2"/>
     <sheet name="onshoreWind" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -41,6 +41,40 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Jonas Meier</author>
+  </authors>
+  <commentList>
+    <comment ref="A17" authorId="0" shapeId="0" xr:uid="{0DD86A29-3784-4EFD-BCDC-268E8BD41CCB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Jonas Meier:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+scenic areas, forest parks, geoparks, and 5 A tourist attraction</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Jonas Meier</author>
@@ -98,47 +132,13 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Jonas Meier</author>
-  </authors>
-  <commentList>
-    <comment ref="A15" authorId="0" shapeId="0" xr:uid="{0DD86A29-3784-4EFD-BCDC-268E8BD41CCB}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Jonas Meier:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-scenic areas, forest parks, geoparks, and 5 A tourist attraction</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Jonas Meier</author>
   </authors>
   <commentList>
-    <comment ref="A16" authorId="0" shapeId="0" xr:uid="{A47730DC-4D19-4B9F-B90E-6F3F7C72568C}">
+    <comment ref="A20" authorId="0" shapeId="0" xr:uid="{A47730DC-4D19-4B9F-B90E-6F3F7C72568C}">
       <text>
         <r>
           <rPr>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="240">
   <si>
     <t>Shen_solarPV_base</t>
   </si>
@@ -719,9 +719,6 @@
     <t>solar, onshorewind, offhsorewind</t>
   </si>
   <si>
-    <t>3000m</t>
-  </si>
-  <si>
     <t>in %, utilization factor
 [0,3]=1
 (3,6]=0.5
@@ -805,9 +802,6 @@
   </si>
   <si>
     <t>Tian2023_solarPV</t>
-  </si>
-  <si>
-    <t>max 5%</t>
   </si>
   <si>
     <t>comment</t>
@@ -973,9 +967,6 @@
     <t>YES</t>
   </si>
   <si>
-    <t>historical sites</t>
-  </si>
-  <si>
     <t>country boarders</t>
   </si>
   <si>
@@ -1033,12 +1024,6 @@
     <t>ESA GlobCover 2009, 300x300m</t>
   </si>
   <si>
-    <t>included:
-- 11, 14, 20, 30, 110, 120
-130, 140, 150, 180, 190,
-200</t>
-  </si>
-  <si>
     <t>GridFinder (2020)</t>
   </si>
   <si>
@@ -1107,9 +1092,6 @@
   </si>
   <si>
     <t>30°</t>
-  </si>
-  <si>
-    <t>200-300</t>
   </si>
   <si>
     <r>
@@ -1241,12 +1223,235 @@
   <si>
     <t>Zink2024</t>
   </si>
+  <si>
+    <t>Spyridonidou2020</t>
+  </si>
+  <si>
+    <t>Systematic Review of Site-Selection
+Processes in Onshore and Offshore 
+Wind Energy Research</t>
+  </si>
+  <si>
+    <t>onshore wind, offshorewind</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3390/en13225906</t>
+  </si>
+  <si>
+    <t>Zink2024_solar</t>
+  </si>
+  <si>
+    <t>Zink2024_wind</t>
+  </si>
+  <si>
+    <t>GIS-based Evaluation of Suitability 
+and Implementation Prospects for 
+Solar PV Energy in Africa</t>
+  </si>
+  <si>
+    <t>Proposing a Methodology to 
+Evaluate the Feasability and
+Implementation Potiential of 
+Wind Energy in Africa Using GIS Data</t>
+  </si>
+  <si>
+    <t>10.1109/PowerAfrica61624.2024.10759357</t>
+  </si>
+  <si>
+    <t>10.1109/PowerAfrica61624.2024.10759431</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/s41597-025-04937-6</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.apenergy.2019.04.005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://doi.org/10.1007/s43979-022-00020-w </t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.eiar.2023.107161</t>
+  </si>
+  <si>
+    <t>resolution</t>
+  </si>
+  <si>
+    <t>mean value, min/max,
+predominant value</t>
+  </si>
+  <si>
+    <t>550, 0/2000, 0</t>
+  </si>
+  <si>
+    <t>4060, 0/17000, 3000</t>
+  </si>
+  <si>
+    <t>18.65%, 10/57.7%, 10%</t>
+  </si>
+  <si>
+    <t>475, 0/4000, 400</t>
+  </si>
+  <si>
+    <t>country boarder</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>5.2, 4/6.5, 5</t>
+  </si>
+  <si>
+    <t>1315, 200/2000, 2000</t>
+  </si>
+  <si>
+    <t>1690, 0/10000, 0</t>
+  </si>
+  <si>
+    <t>750, 0/1000, 1000</t>
+  </si>
+  <si>
+    <t>465, 300/500,500</t>
+  </si>
+  <si>
+    <t>historical/religious sites</t>
+  </si>
+  <si>
+    <t>142, 0/300, 100</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">exclusion:
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>urban &amp; residential:
+1125, 0/3000, 500</t>
+    </r>
+  </si>
+  <si>
+    <t>only using min values
+see paper for 
+differentiated distances</t>
+  </si>
+  <si>
+    <t>5°</t>
+  </si>
+  <si>
+    <t>6.9 m/s</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>exclusion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+- residential: 800
+- industrial: 400
+- snow, ice: 200
+- wetland: 0
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Krauland2024</t>
+  </si>
+  <si>
+    <t>India onshore wind energy
+atlas accounting for altitude
+and land use restrictions and
+co-located solar</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.crsus.2024.100083</t>
+  </si>
+  <si>
+    <t>wind, solar</t>
+  </si>
+  <si>
+    <t>RE Data Explorer</t>
+  </si>
+  <si>
+    <t>OSM, ESRI</t>
+  </si>
+  <si>
+    <t>OSM, WFP on HDX</t>
+  </si>
+  <si>
+    <t>HDX (human data exchange)</t>
+  </si>
+  <si>
+    <t>HDX, OSM, ESRI</t>
+  </si>
+  <si>
+    <t>Unesco, OSM</t>
+  </si>
+  <si>
+    <t>8.61 MW/km² wind turbines</t>
+  </si>
+  <si>
+    <t>10m</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>see publication</t>
+  </si>
+  <si>
+    <t>HH + 0.5 rotor d + 5m (ca205m)</t>
+  </si>
+  <si>
+    <t>205 (canals), 500 (river)</t>
+  </si>
+  <si>
+    <t>5 m/s</t>
+  </si>
+  <si>
+    <t>GWA, GSA</t>
+  </si>
+  <si>
+    <t>SG 3.4-145?</t>
+  </si>
+  <si>
+    <t>literature?</t>
+  </si>
+  <si>
+    <t>see paper</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1288,8 +1493,16 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1299,6 +1512,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1312,10 +1531,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1366,8 +1586,34 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1437,15 +1683,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1751477</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>180689</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>760877</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>114014</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1468,7 +1714,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1381125" y="11420475"/>
+          <a:off x="1666875" y="11544300"/>
           <a:ext cx="8980952" cy="2285714"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1476,6 +1722,129 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1657350</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>506261</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>124894</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="5" name="Group 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{265B4CD8-A696-A1C4-51C3-FD578AC3AFC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="11544300" y="11896725"/>
+          <a:ext cx="11021861" cy="7659169"/>
+          <a:chOff x="11687175" y="11782425"/>
+          <a:chExt cx="10288436" cy="7659169"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="3" name="Picture 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42622EAA-0BB5-D31E-8284-6DEDD9942361}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11687175" y="11782425"/>
+            <a:ext cx="10288436" cy="7659169"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="4" name="TextBox 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{346F3409-84FD-4511-7A05-1858F18278EA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="11696701" y="11791951"/>
+            <a:ext cx="1181100" cy="342900"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="lt1"/>
+          </a:solidFill>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:shade val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="da-DK" sz="1100">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Zink2024</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1743,6 +2112,528 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4EF3672-A950-4BC4-B3DD-995CFFB75543}">
+  <dimension ref="A1:L24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.28515625" customWidth="1"/>
+    <col min="3" max="3" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.42578125" customWidth="1"/>
+    <col min="5" max="5" width="34" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34" style="2" customWidth="1"/>
+    <col min="7" max="7" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="32" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="33.42578125" customWidth="1"/>
+    <col min="12" max="12" width="40.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="L2" s="13" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B3" s="8">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="8">
+        <v>2019</v>
+      </c>
+      <c r="D3" s="8">
+        <v>2022</v>
+      </c>
+      <c r="E3" s="8">
+        <v>2023</v>
+      </c>
+      <c r="F3" s="2">
+        <v>2021</v>
+      </c>
+      <c r="G3" s="14">
+        <v>2022</v>
+      </c>
+      <c r="H3" s="13">
+        <v>2024</v>
+      </c>
+      <c r="I3">
+        <v>2024</v>
+      </c>
+      <c r="J3">
+        <v>2024</v>
+      </c>
+      <c r="K3" s="13">
+        <v>2020</v>
+      </c>
+      <c r="L3">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="K4" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="L4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="L6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="L7" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="H8" t="s">
+        <v>157</v>
+      </c>
+      <c r="L8" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="G9" t="s">
+        <v>145</v>
+      </c>
+      <c r="H9" t="s">
+        <v>157</v>
+      </c>
+      <c r="L9" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="H10" t="s">
+        <v>156</v>
+      </c>
+      <c r="L10" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="H11" t="s">
+        <v>156</v>
+      </c>
+      <c r="L11" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="H12" t="s">
+        <v>12</v>
+      </c>
+      <c r="L12" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="L13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="G14" t="s">
+        <v>144</v>
+      </c>
+      <c r="H14" t="s">
+        <v>157</v>
+      </c>
+      <c r="L14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" t="s">
+        <v>12</v>
+      </c>
+      <c r="L16" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="H17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+    </row>
+    <row r="19" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="G19" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="L19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="H21" t="s">
+        <v>160</v>
+      </c>
+      <c r="L21" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G22" t="s">
+        <v>135</v>
+      </c>
+      <c r="L22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H24" t="s">
+        <v>158</v>
+      </c>
+      <c r="L24" t="s">
+        <v>230</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="K4" r:id="rId1" xr:uid="{B0773972-38D7-41FA-B3C6-0282E57EC2A0}"/>
+    <hyperlink ref="J4" r:id="rId2" display="https://doi.org/10.1109/PowerAfrica61624.2024.10759357" xr:uid="{05EF2060-8417-48A4-981B-6EB18C08027E}"/>
+    <hyperlink ref="I4" r:id="rId3" display="https://doi.org/10.1109/PowerAfrica61624.2024.10759431" xr:uid="{0AAD1AD2-9131-458D-9584-C95DC8ABFF82}"/>
+    <hyperlink ref="B4" r:id="rId4" xr:uid="{EE910AE6-2A22-4EA3-8A07-9060505C25E7}"/>
+    <hyperlink ref="C4" r:id="rId5" xr:uid="{8899C423-C644-4B4B-8F6D-5E8EFC8F715C}"/>
+    <hyperlink ref="D4" r:id="rId6" xr:uid="{A904BA0F-B5BF-4C3D-B599-A23BAFB49CEB}"/>
+    <hyperlink ref="E4" r:id="rId7" xr:uid="{10B4FCA4-9834-44AE-85D7-AFBD27767F75}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
+  <legacyDrawing r:id="rId9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1761,8 +2652,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B1" s="6" t="s">
-        <v>176</v>
+      <c r="B1" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
@@ -1777,63 +2668,63 @@
         <v>79</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>123</v>
+      <c r="A2" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H2" s="10"/>
       <c r="I2" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>126</v>
+      <c r="A3" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>12</v>
@@ -1852,18 +2743,18 @@
         <v>100</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="K3" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>105</v>
+      <c r="A4" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>12</v>
@@ -1875,19 +2766,19 @@
         <v>12</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -1895,7 +2786,7 @@
         <v>13</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C5" s="6">
         <v>5000</v>
@@ -1904,13 +2795,13 @@
         <v>5000</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>99</v>
+        <v>138</v>
+      </c>
+      <c r="G5" s="6">
+        <v>3000</v>
       </c>
       <c r="I5" s="6">
         <v>1750</v>
@@ -1927,7 +2818,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C6" s="9">
         <v>0.2</v>
@@ -1936,22 +2827,22 @@
         <v>0.2</v>
       </c>
       <c r="F6" s="9"/>
-      <c r="G6" s="7" t="s">
-        <v>104</v>
+      <c r="G6" s="26">
+        <v>0.05</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="J6" s="9">
         <v>0.2</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>12</v>
@@ -1972,7 +2863,7 @@
         <v>12</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>12</v>
@@ -1986,7 +2877,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>82</v>
@@ -1995,22 +2886,22 @@
         <v>83</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>84</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -2018,7 +2909,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>12</v>
@@ -2050,7 +2941,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>12</v>
@@ -2071,7 +2962,7 @@
         <v>12</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="K10" s="6">
         <v>100</v>
@@ -2230,8 +3121,8 @@
       <c r="J15" s="6">
         <v>0</v>
       </c>
-      <c r="K15" s="6" t="s">
-        <v>170</v>
+      <c r="K15" s="6">
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -2239,7 +3130,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>12</v>
@@ -2272,7 +3163,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>12</v>
@@ -2304,10 +3195,10 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>128</v>
+        <v>212</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>12</v>
@@ -2421,7 +3312,7 @@
         <v>12</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>12</v>
@@ -2432,7 +3323,7 @@
         <v>32</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>81</v>
@@ -2447,13 +3338,13 @@
         <v>33</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>12</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>12</v>
@@ -2465,22 +3356,22 @@
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>66</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -2507,13 +3398,13 @@
         <v>87</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -2524,10 +3415,10 @@
         <v>12</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>37</v>
@@ -2536,13 +3427,13 @@
         <v>38</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -2572,10 +3463,10 @@
         <v>12</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.25">
@@ -2602,13 +3493,13 @@
         <v>34</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -2631,10 +3522,10 @@
         <v>35</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2644,759 +3535,707 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4EF3672-A950-4BC4-B3DD-995CFFB75543}">
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.28515625" customWidth="1"/>
-    <col min="3" max="3" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.42578125" customWidth="1"/>
-    <col min="5" max="5" width="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="120" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="G6" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" t="s">
-        <v>149</v>
-      </c>
-      <c r="G7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="G8" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="G9" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="G10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" t="s">
-        <v>148</v>
-      </c>
-      <c r="G12" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="90" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="G15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="13" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" s="6"/>
-      <c r="G19" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F20" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="G22" t="s">
-        <v>162</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C914AAC-824C-4C04-AF71-3107016F36CA}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" style="6" customWidth="1"/>
-    <col min="3" max="3" width="27.140625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="34.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="6"/>
+    <col min="2" max="2" width="19.140625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" style="6" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="34.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.140625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="28" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="G1" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>124</v>
+        <v>172</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F2" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="6">
+        <v>50</v>
+      </c>
+      <c r="I3" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" s="10">
+        <v>5000</v>
+      </c>
+      <c r="D5" s="10">
+        <v>5000</v>
+      </c>
+      <c r="F5" s="6">
+        <v>3000</v>
+      </c>
+      <c r="G5" s="6">
+        <v>2000</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="6">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="G6" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="I6" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="210" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="H8" s="6">
+        <v>200</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="G9" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="H9" s="6">
+        <v>150</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="C10" s="6">
+        <v>5000</v>
+      </c>
+      <c r="D10" s="6">
+        <v>5000</v>
+      </c>
+      <c r="H10" s="6">
+        <v>3000</v>
+      </c>
+      <c r="I10" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H12" s="6">
+        <v>1500</v>
+      </c>
+      <c r="I12" s="6">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6">
+        <v>0</v>
+      </c>
+      <c r="I14" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="6">
+        <v>200</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="20"/>
+      <c r="B16" s="24"/>
+    </row>
+    <row r="17" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="23">
+        <v>1000</v>
+      </c>
+      <c r="I17" s="23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="23">
+        <v>1000</v>
+      </c>
+      <c r="I18" s="23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" s="6">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="C20" s="6">
+        <v>3000</v>
+      </c>
+      <c r="D20" s="6">
+        <v>3000</v>
+      </c>
+      <c r="H20" s="6">
+        <v>1000</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="10">
-        <v>5000</v>
-      </c>
-      <c r="C3" s="10">
-        <v>5000</v>
-      </c>
-      <c r="E3" s="6">
-        <v>3000</v>
-      </c>
-      <c r="F3" s="6">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="F4" s="9">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="210" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" s="7" t="s">
+      <c r="H22" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+    </row>
+    <row r="26" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="6" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="F7" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="6">
-        <v>5000</v>
-      </c>
-      <c r="C8" s="6">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="6">
-        <v>0</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0</v>
-      </c>
-      <c r="D12" s="6">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0</v>
-      </c>
-      <c r="F12" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="6">
-        <v>0</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="6">
-        <v>3000</v>
-      </c>
-      <c r="C16" s="6">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="2"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-    </row>
-    <row r="21" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-    </row>
-    <row r="23" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="H29" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I29" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="12" t="s">
+      <c r="B31" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" s="12" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+      <c r="H31" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29" s="7" t="s">
+      <c r="B32" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>112</v>
+      <c r="F32" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>